--- a/artfynd/A 20617-2023 artfynd.xlsx
+++ b/artfynd/A 20617-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118767928</v>
       </c>
       <c r="B2" t="n">
-        <v>97752</v>
+        <v>97759</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 20617-2023 artfynd.xlsx
+++ b/artfynd/A 20617-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,1812 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118991341</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79572</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>531920</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6945835</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118991266</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98187</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>532114</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6945544</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118991268</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79572</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>532114</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6945544</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118991362</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100114</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>532081</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6945635</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118991350</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97759</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>504</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>532096</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6945662</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118991364</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103356</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>532081</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6945635</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118991369</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100024</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>532080</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6945642</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118991371</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97759</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>504</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>532084</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6945649</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118991338</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100024</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>531966</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6945716</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118991267</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79601</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>532114</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6945544</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118991360</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98187</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>532081</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6945635</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118991387</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98187</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>532064</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6945607</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118991271</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97876</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>532146</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6945526</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118991355</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97759</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>504</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>532085</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6945628</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118991336</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100024</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>531959</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6945714</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118991357</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100024</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>532078</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6945627</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118991346</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97759</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>504</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lillberget, Fasika, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>532092</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6945680</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
